--- a/TESTS/zlit_7_robin_hud.xlsx
+++ b/TESTS/zlit_7_robin_hud.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -561,6 +561,11 @@
           <t>Тип</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ГР</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -603,6 +608,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -622,7 +632,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Англійський і шотландський фольклор середньовіччя — вони складались і виконувались народними співцями</t>
+          <t>Англійський і шотландський фольклор середньовіччя</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -643,6 +653,11 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -687,6 +702,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -729,6 +749,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -748,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>В лісі Шервуд поблизу Ноттінгема — ліс є символом свободи і рівності поза феодальними законами</t>
+          <t>В лісі Шервуд поблизу Ноттінгема</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -769,6 +794,11 @@
       <c r="H6" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -790,7 +820,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ноттінгемський шериф — символ жорстокого і корумпованого феодального закону</t>
+          <t>Ноттінгемський шериф</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -811,6 +841,11 @@
       <c r="H7" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -832,7 +867,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Маленький Джон брат Тук Мейд Маріан та інші «мерії люди» — вільна спільнота рівних</t>
+          <t>Маленький Джон брат Тук Мейд Маріан та інші «мерії люди»</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -853,6 +888,11 @@
       <c r="H8" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -874,7 +914,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Вірність і силу — попри іронічне ім'я він найбільший і найсильніший серед мерих людей</t>
+          <t>Вірність і силу</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -895,6 +935,11 @@
       <c r="H9" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -916,7 +961,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Монаха що порушив монастирський спосіб життя і приєднався до вільних людей — символ бунту проти церковної корупції</t>
+          <t>Монаха що порушив монастирський спосіб життя і приєднався до вільних людей</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -937,6 +982,11 @@
       <c r="H10" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -948,37 +998,42 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 1)</t>
+          <t>Яку зброю вважають символом Робіна Гуда і в чому його майстерність?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Меч</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Лук і стріли — він найкращий лучник в Англії, що б'є в ціль на неймовірну відстань</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Спис</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Щит</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -990,37 +1045,42 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 2)</t>
+          <t>Яке повне ім'я носив Робін Гуд за деякими баладами?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Робін з Локслі</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Робін з Локслі або граф Гантінгтон — залежно від варіанту балади</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Роберт Худ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вільям Гуд</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1032,37 +1092,42 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 3)</t>
+          <t>Чому Робін Гуд оселився в лісі Шервуд, а не жив у місті чи селі?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він любив природу</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Несправедливий закон поставив його поза законом, і ліс став єдиним прихистком вільних людей</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Ліс здавався дешевшим</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він не хотів платити оренду</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1074,37 +1139,42 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 1)</t>
+          <t>Хто такий Маленький Джон і звідки він отримав своє ім'я?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Справді маленький чоловік</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Величезний і дужий чоловік — ім'я іронічне, бо він насправді найбільший серед усіх</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Молодший брат Джона</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Джон-молодший на відміну від старшого</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1116,37 +1186,42 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 2)</t>
+          <t>Яка роль Маленького Джона у загоні?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Кухар</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Найближчий товариш і правиця Робіна, зразок вірності та сили</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Скарбник</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Розвідник</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1158,37 +1233,42 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 3)</t>
+          <t>За якою баладою Маленький Джон і Робін спершу зустрілись?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Їх познайомив брат Тук</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Вони зустрілись на вузькому мосту через струмок і довго билися жердинами</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Їх звела Маріан</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вони разом росли</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1200,37 +1280,42 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 1)</t>
+          <t>Хто такий брат Тук і чому він приєднався до загону?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Слуга шерифа</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Веселий і войовничий монах, що полюбив більше волю лісу, ніж монастирську замкненість</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Лісовий трактирник</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Шериф у минулому</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1242,37 +1327,42 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 2)</t>
+          <t>Яку роль відіграє Мейд Маріан у баладах?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Ворожа до Робіна</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Кохана Робіна, шляхетна і сміілива жінка — символ того, що він захищає і для чого бореться</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Служниця шерифа</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Другорядний персонаж без ролі</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1284,37 +1374,42 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 3)</t>
+          <t>Чим цінний образ Мейд Маріан у порівнянні з більшістю жіночих образів середньовічних балад?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Нічим особливим</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Вона активна і сміілива, а не пасивна жертва чи нагорода</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вона магічна постать</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вона правителька</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1326,37 +1421,42 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 1)</t>
+          <t>Якою соціальною несправедливістю найбільше займався Робін Гуд у баладах?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Боровся з іноземними загарбниками</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Захищав бідних від непомірних податків і свавілля шерифа та церковних чиновників</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Звільняв в'язнів тюрем</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Допомагав купцям</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1368,37 +1468,42 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 2)</t>
+          <t>Як Робін Гуд ставився до священиків-корупціонерів у баладах?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>З повагою до будь-яких священиків</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Грабував жадібних єпископів і абатів, але поважав бідних і чесних</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Ненавидів усе духовенство</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Ніяк не ставився</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1410,37 +1515,42 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 3)</t>
+          <t>У чому різниця між ставленням Робіна до простолюдину і до багатіїв у баладах?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він ставився однаково до всіх</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Бідних захищав і ділився з ними, а з багатих і корумпованих брав силою</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він грабував усіх</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він не робив різниці</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1452,37 +1562,42 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 1)</t>
+          <t>Що таке «благородний розбійник» як літературний тип і ким є Робін Гуд у цьому контексті?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Просто злодій</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Герой, що порушує несправедливий закон заради вищої справедливості — Робін Гуд є класичним прикладом</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Офіційний рицар</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Народний суддя</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1494,37 +1609,42 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 2)</t>
+          <t>Яких ще «благородних розбійників» можна знайти у світовій літературі?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Лише Робін Гуд</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Дон Кіхот, Зорро, Арсен Люпен — герої, що борються з несправедливістю поза законом</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Жодних схожих немає</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Лише у народних піснях</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1536,37 +1656,42 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 3)</t>
+          <t>У чому різниця між «народними баладами» і «авторськими баладами»?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Авторські кращі</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Народні — анонімні, передаються усно, змінюються з часом; авторські — зі встановленим автором і текстом</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Народні завжди короткі</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Авторські завжди старіші</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1578,37 +1703,42 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 1)</t>
+          <t>Що символізує образ лісу Шервуд у баладах?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Небезпечне місце</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Простір свободи поза корумпованою феодальною владою — там своя справедливість</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Звичайний ліс</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Місце засідок</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1620,37 +1750,42 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 2)</t>
+          <t>Чому ліс у середньовічному контексті був особливим соціальним місцем?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Там зростали рідкісні рослини</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Ліс стояв поза юрисдикцією феодалів — той, хто жив там, не підпадав під їхній закон</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Там краще клімат</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Там жили монахи</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1662,37 +1797,42 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 3)</t>
+          <t>Як балади про Робіна Гуда ставляться до короля Ричарда I?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Робін ворогує з ним</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Робін поважає законного короля і підтримує його, воюючи лише проти тих, хто зловживає владою у відсутність короля</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Ричард злий персонаж</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Робін байдужий до короля</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1704,37 +1844,42 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 1)</t>
+          <t>Чому образ Робіна Гуда зберігає популярність до сьогодні — у фільмах, книгах, іграх?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Бо він носить зелений костюм</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Бо він втілює вічну мрію про справедливість від несправедливих законів і влади</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Бо про нього написано мало</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Бо він не помер</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1746,37 +1891,42 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 2)</t>
+          <t>Яку соціальну критику несуть балади про Робіна Гуда для сучасного читача?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Ніякої</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Засудження корупції, класової нерівності й несправедливого закону, що служить лише багатим</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Лише критику релігії</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Лише критику короля</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1788,37 +1938,42 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 3)</t>
+          <t>Яка роль жанру балади у збереженні пам'яті про народного героя?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Жодної особливої</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Балади передавались з покоління в покоління, підтримуючи живий образ героя і мрію про справедливість</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Балади менш ефективні за книги</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Лише розважальна</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1843,8 +1998,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>А</t>
@@ -1853,6 +2006,11 @@
       <c r="H32" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1877,8 +2035,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>Б</t>
@@ -1887,6 +2043,11 @@
       <c r="H33" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1911,8 +2072,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>Б</t>
@@ -1921,6 +2080,11 @@
       <c r="H34" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1932,21 +2096,19 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Яка різниця між народними баладами і авторськими?</t>
+          <t>Народні балади — анонімні, передаються усно і змінюються з часом, тоді як авторські мають встановленого автора і фіксований текст.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>А</t>
@@ -1955,6 +2117,11 @@
       <c r="H35" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1966,21 +2133,19 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Чому середньовічний ліс є важливим символом у баладах?</t>
+          <t>Середньовічний ліс у баладах символізує простір свободи поза феодальною владою, а не просто природний ландшафт.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>А</t>
@@ -1989,6 +2154,11 @@
       <c r="H36" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2000,29 +2170,32 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Що спільного між Робіном Гудом і іншими «благородними розбійниками» світової літератури?</t>
+          <t>Робін Гуд є унікальним явищем — жодних схожих образів «благородного розбійника» немає у світовій літературі.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2034,21 +2207,19 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Яким є образ Мейд Маріан у баладах про Робіна Гуда?</t>
+          <t>Мейд Маріан у баладах зображується як активна і смілива жінка, а не пасивна жертва чи нагорода для героя.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>А</t>
@@ -2057,6 +2228,11 @@
       <c r="H38" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2068,21 +2244,19 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Яка головна ідея балад про Робіна Гуда?</t>
+          <t>Головна ідея балад про Робіна Гуда — справедливість важливіша за формальний закон, коли закон служить лише сильним.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>А</t>
@@ -2091,6 +2265,11 @@
       <c r="H39" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2102,29 +2281,32 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Чому образ Робіна Гуда зберігає популярність до сьогодні?</t>
+          <t>Балади про Робіна Гуда популярні лише в Англії і не мають відгуку в інших культурах.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2169,6 +2351,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2211,6 +2398,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2220,27 +2412,27 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Які риси характеру Робіна Гуда роблять його народним героєм?</t>
+          <t>Що робить Робіна Гуда народним героєм балад?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Відвага і майстерність стрільця</t>
+          <t>Майстерність стрільця із лука</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Захист бідних і слабких</t>
+          <t>Захист бідних від свавілля шерифа</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Особисте збагачення</t>
+          <t>Робін Гуд підтримував шерифа Ноттінгема</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Вірність справедливому королю</t>
+          <t>Вірність законному королю Ричарду</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2251,6 +2443,11 @@
       <c r="H43" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2295,6 +2492,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2314,7 +2516,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Грабувати тільки багатих і жорстоких а здобуте роздавати бідним — ідея справедливого перерозподілу</t>
+          <t>Грабувати тільки багатих і жорстоких а здобуте роздавати бідним</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2335,6 +2537,11 @@
       <c r="H45" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2563,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Критику феодальної несправедливості і корупції духовенства — правда на боці простого народу</t>
+          <t>Критику феодальної несправедливості і корупції духовенства</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2377,6 +2584,11 @@
       <c r="H46" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
